--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -81,7 +81,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284112, 284113</t>
+          <t xml:space="preserve">281195</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -90,7 +90,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>657</v>
+        <v>1490</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,7 +131,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3082942</t>
+          <t xml:space="preserve">282915, 282916</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -140,7 +140,7 @@
         </is>
       </c>
       <c r="F3">
-        <v>2275</v>
+        <v>2700</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3084780</t>
+          <t xml:space="preserve">282930, 282931, 282932</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>300</v>
+        <v>4824</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087704</t>
+          <t xml:space="preserve">284073</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F5">
-        <v>466</v>
+        <v>344</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087714</t>
+          <t xml:space="preserve">284073, 284074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F6">
-        <v>497</v>
+        <v>1427</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087714</t>
+          <t xml:space="preserve">284074</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>1185</v>
+        <v>1850</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117334</t>
+          <t xml:space="preserve">284112, 284113</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>437</v>
+        <v>657</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121470</t>
+          <t xml:space="preserve">284140, 284141</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>312</v>
+        <v>2360</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126776</t>
+          <t xml:space="preserve">284142, 284143</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F10">
-        <v>997</v>
+        <v>2707</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128993</t>
+          <t xml:space="preserve">284572, 284573, 284581, 284574, 284575, 284576, 284577, 284578, 284579, 284580, 284582, 284583, 284584</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>1397</v>
+        <v>5113</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425537</t>
+          <t xml:space="preserve">3082942</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>880</v>
+        <v>2275</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425830</t>
+          <t xml:space="preserve">3087704</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>700</v>
+        <v>466</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">3087714</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F14">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">3087714</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15">
-        <v>1160</v>
+        <v>1185</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431435</t>
+          <t xml:space="preserve">3117334</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F16">
-        <v>558</v>
+        <v>437</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432442</t>
+          <t xml:space="preserve">3121470</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F17">
-        <v>5867</v>
+        <v>312</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">3128993</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>445</v>
+        <v>1397</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7005272</t>
+          <t xml:space="preserve">5425537</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="F19">
-        <v>307</v>
+        <v>880</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070028</t>
+          <t xml:space="preserve">5425830</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F20">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070028</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F21">
-        <v>380</v>
+        <v>526</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">724666, 5428307</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F22">
-        <v>922</v>
+        <v>1160</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">724669, 3140732</t>
+          <t xml:space="preserve">5432442</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F23">
-        <v>656</v>
+        <v>5867</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">724675, 5425934</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F24">
-        <v>1781</v>
+        <v>445</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">724682, 5432419</t>
+          <t xml:space="preserve">7005272</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>433</v>
+        <v>307</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">724694, 3133448</t>
+          <t xml:space="preserve">724666, 5428307</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>351</v>
+        <v>922</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">724695, 5430610</t>
+          <t xml:space="preserve">724669, 3140732</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F27">
-        <v>304</v>
+        <v>656</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">724715, 3140859</t>
+          <t xml:space="preserve">724675, 5425934</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>1604</v>
+        <v>1781</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">724743, 5432958</t>
+          <t xml:space="preserve">724694, 3133448</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F29">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">724745, 5433534</t>
+          <t xml:space="preserve">724715, 3140859</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>313</v>
+        <v>1604</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">724760, 3120350</t>
+          <t xml:space="preserve">724743, 5432958</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">724770, 5437631</t>
+          <t xml:space="preserve">724745, 5433534</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F32">
-        <v>442</v>
+        <v>313</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">724774, 8882553</t>
+          <t xml:space="preserve">724760, 3120350</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">724778, 5438223</t>
+          <t xml:space="preserve">724770, 5437631</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>3500</v>
+        <v>442</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">724782, 5438223</t>
+          <t xml:space="preserve">724774, 8882553</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">724788, 8509565</t>
+          <t xml:space="preserve">724782, 5438223</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F36">
-        <v>320</v>
+        <v>251</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">724796, 8871918</t>
+          <t xml:space="preserve">724788, 8509565</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F37">
-        <v>1097</v>
+        <v>320</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F38">
-        <v>531</v>
+        <v>1097</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">724804, 5439682</t>
+          <t xml:space="preserve">724796, 8871918</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F39">
-        <v>348</v>
+        <v>531</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">724809, 5439846</t>
+          <t xml:space="preserve">724804, 5439682</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>259</v>
+        <v>348</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">724810, 5439200</t>
+          <t xml:space="preserve">724809, 5439846</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>405</v>
+        <v>259</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">724850, 9591135</t>
+          <t xml:space="preserve">724810, 5439200</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">724868, 5432442</t>
+          <t xml:space="preserve">724850, 9591135</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F43">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">724886, 100036307</t>
+          <t xml:space="preserve">724868, 5432442</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F44">
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805120</t>
+          <t xml:space="preserve">724886, 100036307</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">7805120</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">7856562</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F47">
-        <v>517</v>
+        <v>369</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7856562</t>
+          <t xml:space="preserve">8296500</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>369</v>
+        <v>876</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8296500</t>
+          <t xml:space="preserve">724667, 5428309</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2440,21 +2440,21 @@
         </is>
       </c>
       <c r="F49">
-        <v>876</v>
+        <v>894</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100042084</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2014-08-16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">724667, 5428309</t>
+          <t xml:space="preserve">7404279</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>894</v>
+        <v>350</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100042084</t>
+          <t xml:space="preserve">200015231</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014-08-16</t>
+          <t xml:space="preserve">2019-06-17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7404279</t>
+          <t xml:space="preserve">8871914</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="F51">
-        <v>350</v>
+        <v>781</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015231</t>
+          <t xml:space="preserve">200015513</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-17</t>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871914</t>
+          <t xml:space="preserve">3121332</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="F52">
-        <v>781</v>
+        <v>2239</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015513</t>
+          <t xml:space="preserve">200017375</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121332</t>
+          <t xml:space="preserve">3117313</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="F53">
-        <v>2239</v>
+        <v>405</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017375</t>
+          <t xml:space="preserve">200021587</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2686,20 +2686,20 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>405</v>
+        <v>1513</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021587</t>
+          <t xml:space="preserve">200021700</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117313</t>
+          <t xml:space="preserve">3126520</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>1513</v>
+        <v>1648</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021700</t>
+          <t xml:space="preserve">200026621</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-01</t>
+          <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126520</t>
+          <t xml:space="preserve">3139677</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,11 +2790,11 @@
         </is>
       </c>
       <c r="F56">
-        <v>1648</v>
+        <v>536</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026621</t>
+          <t xml:space="preserve">200026632</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139677</t>
+          <t xml:space="preserve">3140034</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,11 +2840,11 @@
         </is>
       </c>
       <c r="F57">
-        <v>536</v>
+        <v>445</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026632</t>
+          <t xml:space="preserve">200026630</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140034</t>
+          <t xml:space="preserve">5432832</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,11 +2890,11 @@
         </is>
       </c>
       <c r="F58">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026630</t>
+          <t xml:space="preserve">200026622</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432832</t>
+          <t xml:space="preserve">3127217</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026622</t>
+          <t xml:space="preserve">200027265</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-12</t>
+          <t xml:space="preserve">2020-01-26</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3127217</t>
+          <t xml:space="preserve">3090872</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="F60">
-        <v>413</v>
+        <v>525</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027265</t>
+          <t xml:space="preserve">200027901</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-26</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3090872</t>
+          <t xml:space="preserve">3131075</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>525</v>
+        <v>310</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027901</t>
+          <t xml:space="preserve">200031114</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">282915, 282916</t>
+          <t xml:space="preserve">3128185</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="F62">
-        <v>2700</v>
+        <v>595</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031113</t>
+          <t xml:space="preserve">200033932</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3131075</t>
+          <t xml:space="preserve">3128276</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031114</t>
+          <t xml:space="preserve">200033931</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128185</t>
+          <t xml:space="preserve">5437923</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,11 +3190,11 @@
         </is>
       </c>
       <c r="F64">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033932</t>
+          <t xml:space="preserve">200033910</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128276</t>
+          <t xml:space="preserve">3089614</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3240,16 +3240,16 @@
         </is>
       </c>
       <c r="F65">
-        <v>263</v>
+        <v>468</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033931</t>
+          <t xml:space="preserve">200034019</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-12</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437923</t>
+          <t xml:space="preserve">5426954</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="F66">
-        <v>600</v>
+        <v>285</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033910</t>
+          <t xml:space="preserve">200034024</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-12</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089614</t>
+          <t xml:space="preserve">3087714</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>468</v>
+        <v>6439</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034019</t>
+          <t xml:space="preserve">200034133</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426954</t>
+          <t xml:space="preserve">5427060</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="F68">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034024</t>
+          <t xml:space="preserve">200034101</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087714</t>
+          <t xml:space="preserve">5431435</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F69">
-        <v>6439</v>
+        <v>558</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034133</t>
+          <t xml:space="preserve">200034801</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427060</t>
+          <t xml:space="preserve">5426815</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034101</t>
+          <t xml:space="preserve">200039507</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2020-10-21</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426815</t>
+          <t xml:space="preserve">8916724</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>319</v>
+        <v>1854</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039507</t>
+          <t xml:space="preserve">200046119</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-21</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916724</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>1854</v>
+        <v>1351</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046119</t>
+          <t xml:space="preserve">200046264</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3636,11 +3636,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>1351</v>
+        <v>372</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3686,11 +3686,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74">
-        <v>372</v>
+        <v>1297</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3736,11 +3736,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F75">
-        <v>1297</v>
+        <v>3739</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">7499758</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>3739</v>
+        <v>396</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046264</t>
+          <t xml:space="preserve">100248354</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-01</t>
+          <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7499758</t>
+          <t xml:space="preserve">7894499</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,11 +3840,11 @@
         </is>
       </c>
       <c r="F77">
-        <v>396</v>
+        <v>3029</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054697</t>
+          <t xml:space="preserve">200054693</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7894499</t>
+          <t xml:space="preserve">3084780</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>3029</v>
+        <v>300</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054693</t>
+          <t xml:space="preserve">200054889</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">3126776</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,11 +3990,11 @@
         </is>
       </c>
       <c r="F80">
-        <v>1407</v>
+        <v>997</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054894</t>
+          <t xml:space="preserve">200054891</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4031,20 +4031,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">5429771</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>1435</v>
+        <v>469</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054882</t>
+          <t xml:space="preserve">200054870</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">724695, 5430610</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F82">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100248967</t>
+          <t xml:space="preserve">200054879</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429771</t>
+          <t xml:space="preserve">724778, 5438223</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>469</v>
+        <v>3500</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054870</t>
+          <t xml:space="preserve">200054865</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">284572, 284573, 284581, 284574, 284575, 284576, 284577, 284578, 284579, 284580, 284582, 284583, 284584</t>
+          <t xml:space="preserve">724682, 5432419</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F85">
-        <v>5113</v>
+        <v>433</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311028075</t>
+          <t xml:space="preserve">310033068</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-22</t>
+          <t xml:space="preserve">2023-04-03</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F121">
-        <v>1804</v>
+        <v>1407</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372868</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F122">
-        <v>260</v>
+        <v>1435</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372889</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F123">
-        <v>2183</v>
+        <v>255</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,20 +6181,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>819</v>
+        <v>1804</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311372868</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6231,20 +6231,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F125">
-        <v>713</v>
+        <v>260</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311372889</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6286,11 +6286,11 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F126">
-        <v>587</v>
+        <v>2183</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6336,11 +6336,11 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F127">
-        <v>691</v>
+        <v>819</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119126</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F128">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381027</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-06</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119126</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F129">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381027</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-06</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437014</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F130">
-        <v>2207</v>
+        <v>691</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384900</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-26</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426499</t>
+          <t xml:space="preserve">3119126</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="F131">
-        <v>500</v>
+        <v>733</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390686</t>
+          <t xml:space="preserve">311381027</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426957</t>
+          <t xml:space="preserve">3119126</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>764</v>
+        <v>612</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390674</t>
+          <t xml:space="preserve">311381027</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">5437014</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F133">
-        <v>1046</v>
+        <v>2207</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390832</t>
+          <t xml:space="preserve">311384900</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2029-06-26</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432446</t>
+          <t xml:space="preserve">5426499</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>1545</v>
+        <v>500</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390778</t>
+          <t xml:space="preserve">311390686</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7825651</t>
+          <t xml:space="preserve">5426957</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F135">
-        <v>1003</v>
+        <v>764</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390824</t>
+          <t xml:space="preserve">311390674</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,20 +6781,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9859610</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F136">
-        <v>1166</v>
+        <v>1046</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390820</t>
+          <t xml:space="preserve">311390832</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425830</t>
+          <t xml:space="preserve">5432446</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>320</v>
+        <v>1545</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391046</t>
+          <t xml:space="preserve">311390778</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-01</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085359</t>
+          <t xml:space="preserve">7825651</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="F138">
-        <v>407</v>
+        <v>1003</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392991</t>
+          <t xml:space="preserve">311390824</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-15</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438878</t>
+          <t xml:space="preserve">9859610</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>623</v>
+        <v>1166</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421941</t>
+          <t xml:space="preserve">311390820</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-11</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437745</t>
+          <t xml:space="preserve">5425830</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>5144</v>
+        <v>320</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424091</t>
+          <t xml:space="preserve">311391046</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2029-08-01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871869</t>
+          <t xml:space="preserve">3085359</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>280</v>
+        <v>407</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311431448</t>
+          <t xml:space="preserve">311392991</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-02</t>
+          <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">5438878</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F142">
-        <v>2572</v>
+        <v>623</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311421939</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2030-02-11</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">5437745</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>930</v>
+        <v>5144</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311424091</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">8871869</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F144">
-        <v>2111</v>
+        <v>280</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311431448</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2030-04-02</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7236,15 +7236,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145">
-        <v>890</v>
+        <v>2572</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438857</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F146">
-        <v>1384</v>
+        <v>930</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F147">
-        <v>1725</v>
+        <v>2111</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F148">
-        <v>1245</v>
+        <v>890</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311438857</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7436,11 +7436,11 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F149">
-        <v>1098</v>
+        <v>1384</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7481,20 +7481,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424711</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F150">
-        <v>1470</v>
+        <v>1725</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473578</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085399</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F151">
-        <v>361</v>
+        <v>1245</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540217</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085399</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F152">
-        <v>260</v>
+        <v>1098</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540213</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">284073, 284074</t>
+          <t xml:space="preserve">5424711</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>1427</v>
+        <v>1470</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558490</t>
+          <t xml:space="preserve">311473578</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">284074</t>
+          <t xml:space="preserve">3085399</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>1850</v>
+        <v>361</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558489</t>
+          <t xml:space="preserve">311540217</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5439361</t>
+          <t xml:space="preserve">3085399</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F155">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558487</t>
+          <t xml:space="preserve">311540213</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">284073</t>
+          <t xml:space="preserve">5439361</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558757</t>
+          <t xml:space="preserve">311558487</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-30</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432801</t>
+          <t xml:space="preserve">7070028</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F203">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598252</t>
+          <t xml:space="preserve">311595275</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438675</t>
+          <t xml:space="preserve">7070028</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F204">
-        <v>308</v>
+        <v>380</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598256</t>
+          <t xml:space="preserve">311595275</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438921</t>
+          <t xml:space="preserve">5432801</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F205">
-        <v>1785</v>
+        <v>332</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601329</t>
+          <t xml:space="preserve">311598249</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8923613</t>
+          <t xml:space="preserve">5438675</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -10290,16 +10290,16 @@
         </is>
       </c>
       <c r="F206">
-        <v>1056</v>
+        <v>308</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601326</t>
+          <t xml:space="preserve">311598256</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,20 +10331,20 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8923613</t>
+          <t xml:space="preserve">5438921</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F207">
-        <v>556</v>
+        <v>1785</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601326</t>
+          <t xml:space="preserve">311601329</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437394</t>
+          <t xml:space="preserve">8923613</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10390,16 +10390,16 @@
         </is>
       </c>
       <c r="F208">
-        <v>559</v>
+        <v>1056</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602191</t>
+          <t xml:space="preserve">311601326</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-22</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113302</t>
+          <t xml:space="preserve">8923613</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F209">
-        <v>914</v>
+        <v>556</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602192</t>
+          <t xml:space="preserve">311601326</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-22</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3083012</t>
+          <t xml:space="preserve">5437394</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603710</t>
+          <t xml:space="preserve">311602191</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-29</t>
+          <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425509</t>
+          <t xml:space="preserve">9113302</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F211">
-        <v>1739</v>
+        <v>914</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605488</t>
+          <t xml:space="preserve">311602192</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-06</t>
+          <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3082296</t>
+          <t xml:space="preserve">3083012</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="F212">
-        <v>905</v>
+        <v>536</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609230</t>
+          <t xml:space="preserve">311603710</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-05-29</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091013</t>
+          <t xml:space="preserve">5425509</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F213">
-        <v>441</v>
+        <v>1739</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609231</t>
+          <t xml:space="preserve">311605488</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-06</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,20 +10681,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091013</t>
+          <t xml:space="preserve">3082296</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F214">
-        <v>422</v>
+        <v>905</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609232</t>
+          <t xml:space="preserve">311609230</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5436979</t>
+          <t xml:space="preserve">3091013</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -10740,11 +10740,11 @@
         </is>
       </c>
       <c r="F215">
-        <v>2621</v>
+        <v>441</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609233</t>
+          <t xml:space="preserve">311609231</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">3091013</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F216">
-        <v>330</v>
+        <v>422</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611330</t>
+          <t xml:space="preserve">311609232</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">5436979</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F217">
-        <v>717</v>
+        <v>2621</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611332</t>
+          <t xml:space="preserve">311609233</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F218">
-        <v>773</v>
+        <v>444</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611334</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10931,20 +10931,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F219">
-        <v>418</v>
+        <v>287</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611336</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10981,20 +10981,20 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F220">
-        <v>293</v>
+        <v>496</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611377</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11031,20 +11031,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F221">
-        <v>714</v>
+        <v>1245</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611340</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11086,20 +11086,20 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>469</v>
+        <v>330</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611342</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F223">
-        <v>444</v>
+        <v>1380</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F224">
-        <v>287</v>
+        <v>1396</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615354</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11240,16 +11240,16 @@
         </is>
       </c>
       <c r="F225">
-        <v>496</v>
+        <v>2143</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615356</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F226">
-        <v>1245</v>
+        <v>717</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11336,20 +11336,20 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F227">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611832</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-29</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11386,15 +11386,15 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F228">
-        <v>1380</v>
+        <v>773</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11436,15 +11436,15 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F229">
-        <v>1396</v>
+        <v>418</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615354</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -11486,15 +11486,15 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="F230">
-        <v>2143</v>
+        <v>293</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615356</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432176</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F231">
-        <v>9644</v>
+        <v>714</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311621577</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-19</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">3132020</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="F232">
-        <v>780</v>
+        <v>517</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635811</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-14</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,25 +11631,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9972154</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F233">
-        <v>724</v>
+        <v>469</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635794</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-14</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F234">
-        <v>521</v>
+        <v>304</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643816</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,25 +11731,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">5432176</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F235">
-        <v>1064</v>
+        <v>9644</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643817</t>
+          <t xml:space="preserve">311621577</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,25 +11781,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">3132020</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F236">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643819</t>
+          <t xml:space="preserve">311635811</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">9972154</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F237">
-        <v>784</v>
+        <v>724</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643820</t>
+          <t xml:space="preserve">311635794</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11886,15 +11886,15 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F238">
-        <v>784</v>
+        <v>521</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643821</t>
+          <t xml:space="preserve">311643816</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -11936,15 +11936,15 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F239">
-        <v>784</v>
+        <v>1064</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643823</t>
+          <t xml:space="preserve">311643817</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F240">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643824</t>
+          <t xml:space="preserve">311643819</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12031,25 +12031,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">3132005</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F241">
-        <v>1858</v>
+        <v>784</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645850</t>
+          <t xml:space="preserve">311643820</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725887</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F242">
-        <v>729</v>
+        <v>784</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645849</t>
+          <t xml:space="preserve">311643821</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,25 +12131,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725887</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F243">
-        <v>1856</v>
+        <v>784</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645849</t>
+          <t xml:space="preserve">311643823</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,25 +12181,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">282930, 282931, 282932</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F244">
-        <v>4824</v>
+        <v>784</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651096</t>
+          <t xml:space="preserve">311643824</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079884</t>
+          <t xml:space="preserve">3132005</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -12240,16 +12240,16 @@
         </is>
       </c>
       <c r="F245">
-        <v>330</v>
+        <v>1858</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697414</t>
+          <t xml:space="preserve">311645850</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437545</t>
+          <t xml:space="preserve">9725887</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -12290,16 +12290,16 @@
         </is>
       </c>
       <c r="F246">
-        <v>1266</v>
+        <v>729</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730401</t>
+          <t xml:space="preserve">311645849</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,25 +12331,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">284140, 284141</t>
+          <t xml:space="preserve">9725887</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F247">
-        <v>2360</v>
+        <v>1856</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746899</t>
+          <t xml:space="preserve">311645849</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">284142, 284143</t>
+          <t xml:space="preserve">3079884</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -12390,16 +12390,16 @@
         </is>
       </c>
       <c r="F248">
-        <v>2707</v>
+        <v>330</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311747829</t>
+          <t xml:space="preserve">311697414</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-25</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">281195</t>
+          <t xml:space="preserve">5437545</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -12440,16 +12440,16 @@
         </is>
       </c>
       <c r="F249">
-        <v>1490</v>
+        <v>1266</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311765634</t>
+          <t xml:space="preserve">311730401</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-11</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">

--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åmarksvej 5A</t>
+          <t xml:space="preserve">Dosseringen 6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281195</t>
+          <t xml:space="preserve">724796, 8871918</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H2">
-        <v>1490</v>
+        <v>1097</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 35</t>
+          <t xml:space="preserve">Dosseringen 6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282915, 282916</t>
+          <t xml:space="preserve">724796, 8871918</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H3">
-        <v>2700</v>
+        <v>531</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,17 +211,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalkbrænderivej 5</t>
+          <t xml:space="preserve">Fejøgade 18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">282930, 282931, 282932</t>
+          <t xml:space="preserve">724675, 5425934</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>4824</v>
+        <v>1781</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 7</t>
+          <t xml:space="preserve">Femøgade 4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">284073</t>
+          <t xml:space="preserve">724666, 5428307</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>344</v>
+        <v>922</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 7</t>
+          <t xml:space="preserve">Frisegade 25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">284073, 284074</t>
+          <t xml:space="preserve">7856562</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>1427</v>
+        <v>369</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 7</t>
+          <t xml:space="preserve">Fromsgade 27D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">284074</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H7">
-        <v>1850</v>
+        <v>526</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,17 +451,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 50</t>
+          <t xml:space="preserve">Grønsundsvej 318</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4871</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">284112, 284113</t>
+          <t xml:space="preserve">3128993</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>657</v>
+        <v>1397</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 26</t>
+          <t xml:space="preserve">Guldborgvej 228</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4862</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">284140, 284141</t>
+          <t xml:space="preserve">3082942</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>2360</v>
+        <v>2275</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skerrisvej 24</t>
+          <t xml:space="preserve">Guldborgvej 352</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4862</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">284142, 284143</t>
+          <t xml:space="preserve">724788, 8509565</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H10">
-        <v>2707</v>
+        <v>320</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 3</t>
+          <t xml:space="preserve">Havnegade 6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">284572, 284573, 284581, 284574, 284575, 284576, 284577, 284578, 284579, 284580, 284582, 284583, 284584</t>
+          <t xml:space="preserve">724770, 5437631</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H11">
-        <v>5113</v>
+        <v>442</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 228</t>
+          <t xml:space="preserve">Kirkevej 19B</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4862</t>
+          <t xml:space="preserve">4872</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3082942</t>
+          <t xml:space="preserve">724850, 9591135</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H12">
-        <v>2275</v>
+        <v>361</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundby Alle 99</t>
+          <t xml:space="preserve">Kringelborg Alle 5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087704</t>
+          <t xml:space="preserve">724715, 3140859</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>466</v>
+        <v>1604</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stødstrupvej 1A</t>
+          <t xml:space="preserve">Linde Alle 44</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117334</t>
+          <t xml:space="preserve">7805120</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>437</v>
+        <v>294</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigvej 2</t>
+          <t xml:space="preserve">Linde Alle 50</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121470</t>
+          <t xml:space="preserve">284112, 284113</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>312</v>
+        <v>657</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønsundsvej 318</t>
+          <t xml:space="preserve">Møllebakken 9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4871</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128993</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H18">
-        <v>1397</v>
+        <v>1160</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 21A</t>
+          <t xml:space="preserve">Møllestræde 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425537</t>
+          <t xml:space="preserve">724804, 5439682</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="H19">
-        <v>880</v>
+        <v>348</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 6</t>
+          <t xml:space="preserve">Nr Alslev Stationsvej 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425830</t>
+          <t xml:space="preserve">724760, 3120350</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>700</v>
+        <v>385</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fromsgade 27D</t>
+          <t xml:space="preserve">Nr. Ørslev Bygade 23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">7005272</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>526</v>
+        <v>307</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 9</t>
+          <t xml:space="preserve">Nørre Boulevard 4A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">5432442</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H22">
-        <v>1160</v>
+        <v>5867</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 4A</t>
+          <t xml:space="preserve">Nørregade 21A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432442</t>
+          <t xml:space="preserve">5425537</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>5867</v>
+        <v>880</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvænget 4</t>
+          <t xml:space="preserve">P Hansens Vej 10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">724782, 5438223</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H24">
-        <v>445</v>
+        <v>251</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr. Ørslev Bygade 23</t>
+          <t xml:space="preserve">Poul Martin Møllersvej 10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7005272</t>
+          <t xml:space="preserve">724868, 5432442</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H25">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,26 +1531,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Femøgade 4</t>
+          <t xml:space="preserve">Rådhusvænget 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">724666, 5428307</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H26">
-        <v>922</v>
+        <v>445</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 123C</t>
+          <t xml:space="preserve">Skansevej 17B</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">724669, 3140732</t>
+          <t xml:space="preserve">724745, 5433534</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H27">
-        <v>656</v>
+        <v>313</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fejøgade 18</t>
+          <t xml:space="preserve">Skerrisvej 22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">724675, 5425934</t>
+          <t xml:space="preserve">8296500</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="H28">
-        <v>1781</v>
+        <v>876</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubmøllevej 8</t>
+          <t xml:space="preserve">Smedevænget 30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">724694, 3133448</t>
+          <t xml:space="preserve">724809, 5439846</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H29">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kringelborg Alle 5</t>
+          <t xml:space="preserve">Stadionvej 1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">724715, 3140859</t>
+          <t xml:space="preserve">724774, 8882553</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H30">
-        <v>1604</v>
+        <v>304</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1891,17 +1891,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 17B</t>
+          <t xml:space="preserve">Stubmøllevej 8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">724745, 5433534</t>
+          <t xml:space="preserve">724694, 3133448</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="H32">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Alslev Stationsvej 3</t>
+          <t xml:space="preserve">Stødstrupvej 1A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">724760, 3120350</t>
+          <t xml:space="preserve">3117334</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H33">
-        <v>385</v>
+        <v>437</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 6</t>
+          <t xml:space="preserve">Sundby Alle 99</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">724770, 5437631</t>
+          <t xml:space="preserve">3087704</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 1</t>
+          <t xml:space="preserve">Tuemosevej 8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">724774, 8882553</t>
+          <t xml:space="preserve">724810, 5439200</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>304</v>
+        <v>405</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,26 +2131,26 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">P Hansens Vej 10</t>
+          <t xml:space="preserve">Vendersgade 6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">724782, 5438223</t>
+          <t xml:space="preserve">5425830</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H36">
-        <v>251</v>
+        <v>700</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 352</t>
+          <t xml:space="preserve">Vigvej 2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4862</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">724788, 8509565</t>
+          <t xml:space="preserve">3121470</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H37">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dosseringen 6</t>
+          <t xml:space="preserve">Østergade 57</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">724796, 8871918</t>
+          <t xml:space="preserve">724886, 100036307</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>1097</v>
+        <v>255</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dosseringen 6</t>
+          <t xml:space="preserve">Østre Alle 123C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">724796, 8871918</t>
+          <t xml:space="preserve">724669, 3140732</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>531</v>
+        <v>656</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllestræde 2</t>
+          <t xml:space="preserve">Askøgade 3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">724804, 5439682</t>
+          <t xml:space="preserve">724667, 5428309</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="H40">
-        <v>348</v>
+        <v>894</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100042084</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2014-08-16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedevænget 30</t>
+          <t xml:space="preserve">Sportsvej 1A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4871</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">724809, 5439846</t>
+          <t xml:space="preserve">7404279</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="H41">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200015231</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-17</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuemosevej 8</t>
+          <t xml:space="preserve">Dosseringen 3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">724810, 5439200</t>
+          <t xml:space="preserve">8871914</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="H42">
-        <v>405</v>
+        <v>781</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200015513</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2551,40 +2551,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 19B</t>
+          <t xml:space="preserve">Vigvej 8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4872</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">724850, 9591135</t>
+          <t xml:space="preserve">3121332</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>361</v>
+        <v>2239</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017375</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2611,40 +2611,40 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poul Martin Møllersvej 10</t>
+          <t xml:space="preserve">Eskilstrup Vestergade 62</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">724868, 5432442</t>
+          <t xml:space="preserve">3117313</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200021587</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 57</t>
+          <t xml:space="preserve">Eskilstrup Vestergade 62</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">724886, 100036307</t>
+          <t xml:space="preserve">3117313</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>255</v>
+        <v>1513</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200021700</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 44</t>
+          <t xml:space="preserve">Adelgade 13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7805120</t>
+          <t xml:space="preserve">5432832</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="H46">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026622</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frisegade 25</t>
+          <t xml:space="preserve">Gedser Landevej 59</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4874</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7856562</t>
+          <t xml:space="preserve">3126520</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,21 +2810,21 @@
         </is>
       </c>
       <c r="H47">
-        <v>369</v>
+        <v>1648</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026621</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skerrisvej 22</t>
+          <t xml:space="preserve">Stovbyvej 3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8296500</t>
+          <t xml:space="preserve">3140034</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="H48">
-        <v>876</v>
+        <v>445</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026630</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askøgade 3</t>
+          <t xml:space="preserve">Thorsvej 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">724667, 5428309</t>
+          <t xml:space="preserve">3139677</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,16 +2930,16 @@
         </is>
       </c>
       <c r="H49">
-        <v>894</v>
+        <v>536</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100042084</t>
+          <t xml:space="preserve">200026632</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014-08-16</t>
+          <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1A</t>
+          <t xml:space="preserve">Sortevej 21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4871</t>
+          <t xml:space="preserve">4874</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7404279</t>
+          <t xml:space="preserve">3127217</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,16 +2990,16 @@
         </is>
       </c>
       <c r="H50">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015231</t>
+          <t xml:space="preserve">200027265</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-17</t>
+          <t xml:space="preserve">2020-01-26</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dosseringen 3</t>
+          <t xml:space="preserve">St Kirkestræde 5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4894</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871914</t>
+          <t xml:space="preserve">3090872</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>781</v>
+        <v>525</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015513</t>
+          <t xml:space="preserve">200027901</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigvej 8</t>
+          <t xml:space="preserve">Søndergade 35</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121332</t>
+          <t xml:space="preserve">282915, 282916</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="H52">
-        <v>2239</v>
+        <v>2700</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017375</t>
+          <t xml:space="preserve">200031113</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrup Vestergade 62</t>
+          <t xml:space="preserve">Østergade 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4872</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117313</t>
+          <t xml:space="preserve">3131075</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021587</t>
+          <t xml:space="preserve">200031114</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,35 +3211,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskilstrup Vestergade 62</t>
+          <t xml:space="preserve">Fabriksvej 5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117313</t>
+          <t xml:space="preserve">5437923</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>1513</v>
+        <v>600</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021700</t>
+          <t xml:space="preserve">200033910</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-01</t>
+          <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gedser Landevej 59</t>
+          <t xml:space="preserve">Skolegade 2A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126520</t>
+          <t xml:space="preserve">3128276</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="H55">
-        <v>1648</v>
+        <v>263</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026621</t>
+          <t xml:space="preserve">200033931</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-12</t>
+          <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsvej 2</t>
+          <t xml:space="preserve">Skolegade 2B</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4874</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139677</t>
+          <t xml:space="preserve">3128185</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026632</t>
+          <t xml:space="preserve">200033932</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-12</t>
+          <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stovbyvej 3</t>
+          <t xml:space="preserve">Torebyvej 15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4891</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140034</t>
+          <t xml:space="preserve">3089614</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026630</t>
+          <t xml:space="preserve">200034019</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-12</t>
+          <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 13</t>
+          <t xml:space="preserve">Nørre Boulevard 65C</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432832</t>
+          <t xml:space="preserve">5426954</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3470,16 +3470,16 @@
         </is>
       </c>
       <c r="H58">
-        <v>379</v>
+        <v>285</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026622</t>
+          <t xml:space="preserve">200034024</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-12</t>
+          <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sortevej 21</t>
+          <t xml:space="preserve">Aarslewsgade 5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4874</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3127217</t>
+          <t xml:space="preserve">5427060</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="H59">
-        <v>413</v>
+        <v>296</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027265</t>
+          <t xml:space="preserve">200034101</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-26</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,17 +3571,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">St Kirkestræde 5</t>
+          <t xml:space="preserve">Linde Alle 36</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4894</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3090872</t>
+          <t xml:space="preserve">3087714</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>525</v>
+        <v>6439</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027901</t>
+          <t xml:space="preserve">200034133</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 1</t>
+          <t xml:space="preserve">Poul Martin Møllersvej 1C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4872</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3131075</t>
+          <t xml:space="preserve">5431435</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H61">
-        <v>310</v>
+        <v>558</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200031114</t>
+          <t xml:space="preserve">200034801</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,17 +3691,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2B</t>
+          <t xml:space="preserve">Baagøesgade 17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4874</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128185</t>
+          <t xml:space="preserve">5426815</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="H62">
-        <v>595</v>
+        <v>319</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033932</t>
+          <t xml:space="preserve">200039507</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-12</t>
+          <t xml:space="preserve">2020-10-21</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2A</t>
+          <t xml:space="preserve">Stationsvej 57</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4874</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3128276</t>
+          <t xml:space="preserve">8916724</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="H63">
-        <v>263</v>
+        <v>1854</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033931</t>
+          <t xml:space="preserve">200046119</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-12</t>
+          <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabriksvej 5</t>
+          <t xml:space="preserve">Fromsgade 27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437923</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H64">
-        <v>600</v>
+        <v>1297</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033910</t>
+          <t xml:space="preserve">200046264</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-12</t>
+          <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,17 +3871,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torebyvej 15</t>
+          <t xml:space="preserve">Fromsgade 27A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3089614</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="H65">
-        <v>468</v>
+        <v>1351</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034019</t>
+          <t xml:space="preserve">200046264</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-13</t>
+          <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 65C</t>
+          <t xml:space="preserve">Fromsgade 27B</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426954</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>285</v>
+        <v>372</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034024</t>
+          <t xml:space="preserve">200046264</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-14</t>
+          <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 36</t>
+          <t xml:space="preserve">Fromsgade 27C</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087714</t>
+          <t xml:space="preserve">5426025</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H67">
-        <v>6439</v>
+        <v>3739</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034133</t>
+          <t xml:space="preserve">200046264</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aarslewsgade 5</t>
+          <t xml:space="preserve">Kringelborg Alle 3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427060</t>
+          <t xml:space="preserve">7894499</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>296</v>
+        <v>3029</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034101</t>
+          <t xml:space="preserve">200054693</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poul Martin Møllersvej 1C</t>
+          <t xml:space="preserve">Ndr Ringvej 29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431435</t>
+          <t xml:space="preserve">7499758</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>558</v>
+        <v>396</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034801</t>
+          <t xml:space="preserve">200054697</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-02</t>
+          <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baagøesgade 17</t>
+          <t xml:space="preserve">Møllevej 33A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426815</t>
+          <t xml:space="preserve">3085726</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="H70">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039507</t>
+          <t xml:space="preserve">200054868</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-21</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 57</t>
+          <t xml:space="preserve">Nordby Allé 2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916724</t>
+          <t xml:space="preserve">9486596</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>1854</v>
+        <v>7028</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046119</t>
+          <t xml:space="preserve">200054883</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-25</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fromsgade 27A</t>
+          <t xml:space="preserve">Nystedvej 54A</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">3084780</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>1351</v>
+        <v>300</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046264</t>
+          <t xml:space="preserve">200054889</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-01</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fromsgade 27B</t>
+          <t xml:space="preserve">P Hansens Vej 15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">724778, 5438223</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>372</v>
+        <v>3500</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046264</t>
+          <t xml:space="preserve">200054865</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-01</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fromsgade 27</t>
+          <t xml:space="preserve">Skråvej 2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4874</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">3126776</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>1297</v>
+        <v>997</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046264</t>
+          <t xml:space="preserve">200054891</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-01</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fromsgade 27C</t>
+          <t xml:space="preserve">Vendsysselvej 51</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426025</t>
+          <t xml:space="preserve">5429771</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>3739</v>
+        <v>469</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046264</t>
+          <t xml:space="preserve">200054870</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-01</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Ringvej 29</t>
+          <t xml:space="preserve">Østre Alle 95</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,25 +4541,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7499758</t>
+          <t xml:space="preserve">724695, 5430610</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H76">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100248354</t>
+          <t xml:space="preserve">200054879</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kringelborg Alle 3</t>
+          <t xml:space="preserve">Vestensborg Alle 32</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,25 +4601,25 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7894499</t>
+          <t xml:space="preserve">724682, 5432419</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H77">
-        <v>3029</v>
+        <v>433</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054693</t>
+          <t xml:space="preserve">310033068</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-10</t>
+          <t xml:space="preserve">2023-04-03</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nystedvej 54A</t>
+          <t xml:space="preserve">Torvet 3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3084780</t>
+          <t xml:space="preserve">284572, 284573, 284581, 284574, 284575, 284576, 284577, 284578, 284579, 284580, 284582, 284583, 284584</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>300</v>
+        <v>5113</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054889</t>
+          <t xml:space="preserve">311028075</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2023-11-22</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 33A</t>
+          <t xml:space="preserve">Byvangen 1D</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085726</t>
+          <t xml:space="preserve">3085399</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H79">
-        <v>268</v>
+        <v>476</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054868</t>
+          <t xml:space="preserve">311045170</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2024-03-27</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skråvej 2</t>
+          <t xml:space="preserve">Merkurs Plads 4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4874</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126776</t>
+          <t xml:space="preserve">5432446</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H80">
-        <v>997</v>
+        <v>9400</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054891</t>
+          <t xml:space="preserve">311189121</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendsysselvej 51</t>
+          <t xml:space="preserve">Nr Alslev Langgade 57</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429771</t>
+          <t xml:space="preserve">3119547</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="H81">
-        <v>469</v>
+        <v>285</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054870</t>
+          <t xml:space="preserve">311264382</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4891,45 +4891,45 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 95</t>
+          <t xml:space="preserve">Vigvej 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">724695, 5430610</t>
+          <t xml:space="preserve">3121470</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>304</v>
+        <v>1620</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054879</t>
+          <t xml:space="preserve">311264377</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4951,45 +4951,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">P Hansens Vej 15</t>
+          <t xml:space="preserve">Vigvej 4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">724778, 5438223</t>
+          <t xml:space="preserve">3121470</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>3500</v>
+        <v>1069</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054865</t>
+          <t xml:space="preserve">311264377</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordby Allé 2</t>
+          <t xml:space="preserve">Vigvej 8A</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9486596</t>
+          <t xml:space="preserve">8312266</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,26 +5030,26 @@
         </is>
       </c>
       <c r="H84">
-        <v>7028</v>
+        <v>412</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054883</t>
+          <t xml:space="preserve">311264381</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-16</t>
+          <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestensborg Alle 32</t>
+          <t xml:space="preserve">Niels Hemmingsensvej 4A</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,35 +5081,35 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">724682, 5432419</t>
+          <t xml:space="preserve">5431435</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H85">
-        <v>433</v>
+        <v>933</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">310033068</t>
+          <t xml:space="preserve">311314272</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-03</t>
+          <t xml:space="preserve">2028-05-16</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5131,45 +5131,45 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvangen 1D</t>
+          <t xml:space="preserve">Poul Martin Møllersvej 1B</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085399</t>
+          <t xml:space="preserve">5431435</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H86">
-        <v>476</v>
+        <v>558</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311045170</t>
+          <t xml:space="preserve">311315047</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-03-27</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurs Plads 4</t>
+          <t xml:space="preserve">Parkvej 35</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,35 +5201,35 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432446</t>
+          <t xml:space="preserve">9844842</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H87">
-        <v>9400</v>
+        <v>1639</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311189121</t>
+          <t xml:space="preserve">311323351</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-08</t>
+          <t xml:space="preserve">2028-06-27</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Alslev Langgade 57</t>
+          <t xml:space="preserve">Nr Alslev Langgade 67A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119547</t>
+          <t xml:space="preserve">3120077</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>285</v>
+        <v>638</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264382</t>
+          <t xml:space="preserve">311329673</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigvej 2</t>
+          <t xml:space="preserve">Pandebjergvej 300</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121470</t>
+          <t xml:space="preserve">8275121</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>1620</v>
+        <v>1201</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264377</t>
+          <t xml:space="preserve">311329621</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigvej 4</t>
+          <t xml:space="preserve">Blishøjvej 4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121470</t>
+          <t xml:space="preserve">3139604</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>1069</v>
+        <v>844</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264377</t>
+          <t xml:space="preserve">311330911</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2028-08-16</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vigvej 8A</t>
+          <t xml:space="preserve">Niels Hemmingsensvej 6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8312266</t>
+          <t xml:space="preserve">5431435</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H91">
-        <v>412</v>
+        <v>607</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264381</t>
+          <t xml:space="preserve">311334275</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-03</t>
+          <t xml:space="preserve">2028-09-04</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Hemmingsensvej 4A</t>
+          <t xml:space="preserve">Stødstrupvej 1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431435</t>
+          <t xml:space="preserve">3117332</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H92">
-        <v>933</v>
+        <v>1729</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314272</t>
+          <t xml:space="preserve">311335147</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-16</t>
+          <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poul Martin Møllersvej 1B</t>
+          <t xml:space="preserve">Stødstrupvej 1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431435</t>
+          <t xml:space="preserve">3117332</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H93">
-        <v>558</v>
+        <v>1333</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315047</t>
+          <t xml:space="preserve">311335147</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 35</t>
+          <t xml:space="preserve">Stødstrupvej 1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9844842</t>
+          <t xml:space="preserve">3117332</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H94">
-        <v>1639</v>
+        <v>591</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311323351</t>
+          <t xml:space="preserve">311335147</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-27</t>
+          <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,35 +5671,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Alslev Langgade 67A</t>
+          <t xml:space="preserve">Stødstrupvej 1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3120077</t>
+          <t xml:space="preserve">3117332</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H95">
-        <v>638</v>
+        <v>335</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329673</t>
+          <t xml:space="preserve">311335147</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pandebjergvej 300</t>
+          <t xml:space="preserve">Hospitalsvej 12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8275121</t>
+          <t xml:space="preserve">5431383</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>1201</v>
+        <v>666</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311329621</t>
+          <t xml:space="preserve">311339105</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-09</t>
+          <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,35 +5791,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blishøjvej 4</t>
+          <t xml:space="preserve">Hospitalsvej 14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139604</t>
+          <t xml:space="preserve">5431383</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H97">
-        <v>844</v>
+        <v>425</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330911</t>
+          <t xml:space="preserve">311339105</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-16</t>
+          <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Hemmingsensvej 6</t>
+          <t xml:space="preserve">Vinkelvej 2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431435</t>
+          <t xml:space="preserve">9262753</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>607</v>
+        <v>1077</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311334275</t>
+          <t xml:space="preserve">311339104</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-04</t>
+          <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stødstrupvej 1</t>
+          <t xml:space="preserve">Præstemarken 7</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117332</t>
+          <t xml:space="preserve">5439360</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>1729</v>
+        <v>518</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335147</t>
+          <t xml:space="preserve">311343052</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-10</t>
+          <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stødstrupvej 1</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117332</t>
+          <t xml:space="preserve">5438518</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>1333</v>
+        <v>571</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335147</t>
+          <t xml:space="preserve">311343049</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-10</t>
+          <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stødstrupvej 1</t>
+          <t xml:space="preserve">Torvet 1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117332</t>
+          <t xml:space="preserve">5438518</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>591</v>
+        <v>458</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335147</t>
+          <t xml:space="preserve">311343049</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-10</t>
+          <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stødstrupvej 1</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117332</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H102">
-        <v>335</v>
+        <v>562</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335147</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-10</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospitalsvej 12</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431383</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H103">
-        <v>666</v>
+        <v>2172</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339105</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-01</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hospitalsvej 14</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431383</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H104">
-        <v>425</v>
+        <v>276</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339105</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-01</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,35 +6271,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 2</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9262753</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H105">
-        <v>1077</v>
+        <v>1209</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339104</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-01</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,25 +6341,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438518</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H106">
-        <v>571</v>
+        <v>1072</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343049</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-24</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 1</t>
+          <t xml:space="preserve">Rosenvængets Alle 14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,25 +6401,25 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438518</t>
+          <t xml:space="preserve">7069998</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H107">
-        <v>458</v>
+        <v>1058</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343049</t>
+          <t xml:space="preserve">311347438</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-24</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 7</t>
+          <t xml:space="preserve">Stationspladsen 8</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5439360</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H108">
-        <v>518</v>
+        <v>1716</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311343052</t>
+          <t xml:space="preserve">311351753</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-24</t>
+          <t xml:space="preserve">2028-12-14</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Kongensgade 43</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">8916757</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>562</v>
+        <v>3294</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311352346</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,35 +6571,35 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Rosenvænget 17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">8916757</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>2172</v>
+        <v>1005</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311352331</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,35 +6631,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Ellekildevej 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">8882555</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H111">
-        <v>276</v>
+        <v>5675</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311353436</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-01-04</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,35 +6691,35 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Jernbanegade 24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">5433795</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H112">
-        <v>1209</v>
+        <v>400</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311353757</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-01-08</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,35 +6751,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Kettingevej 78</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4892</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">3082097</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H113">
-        <v>1072</v>
+        <v>1725</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311357593</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-02-01</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Alle 14</t>
+          <t xml:space="preserve">Gartnervej 1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7069998</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H114">
-        <v>1058</v>
+        <v>255</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347438</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationspladsen 8</t>
+          <t xml:space="preserve">Gartnervej 5</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H115">
-        <v>1716</v>
+        <v>1407</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351753</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-14</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 17</t>
+          <t xml:space="preserve">Gartnervej 5</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,25 +6941,25 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916757</t>
+          <t xml:space="preserve">5427386</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H116">
-        <v>1005</v>
+        <v>1435</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352331</t>
+          <t xml:space="preserve">311363577</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,35 +6991,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 43</t>
+          <t xml:space="preserve">Adelgade 61</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916757</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>3294</v>
+        <v>1804</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352346</t>
+          <t xml:space="preserve">311372868</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,35 +7051,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ellekildevej 1</t>
+          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8882555</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118">
-        <v>5675</v>
+        <v>2183</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353436</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-04</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 24</t>
+          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,25 +7121,25 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433795</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H119">
-        <v>400</v>
+        <v>819</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353757</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-08</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingevej 78</t>
+          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4892</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3082097</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H120">
-        <v>1725</v>
+        <v>713</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357593</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-01</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervej 5</t>
+          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H121">
-        <v>1407</v>
+        <v>587</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363577</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervej 5</t>
+          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">5433538</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H122">
-        <v>1435</v>
+        <v>691</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363577</t>
+          <t xml:space="preserve">311372895</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,35 +7351,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnervej 1</t>
+          <t xml:space="preserve">Rådhusvænget 4B</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5427386</t>
+          <t xml:space="preserve">5432902</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H123">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311363577</t>
+          <t xml:space="preserve">311372889</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-08</t>
+          <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 61</t>
+          <t xml:space="preserve">Helene Strangesvej 1</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">3119126</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>1804</v>
+        <v>733</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372868</t>
+          <t xml:space="preserve">311381027</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,35 +7471,35 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvænget 4B</t>
+          <t xml:space="preserve">Helene Strangesvej 1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432902</t>
+          <t xml:space="preserve">3119126</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H125">
-        <v>260</v>
+        <v>612</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372889</t>
+          <t xml:space="preserve">311381027</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
+          <t xml:space="preserve">Rådhusgade 2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5437014</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,16 +7550,16 @@
         </is>
       </c>
       <c r="H126">
-        <v>2183</v>
+        <v>2207</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311384900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-06-26</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
+          <t xml:space="preserve">Hammerlodden 1B</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5426957</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>819</v>
+        <v>764</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311390674</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
+          <t xml:space="preserve">Kongensgade 37</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5426499</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>713</v>
+        <v>500</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311390686</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,35 +7711,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
+          <t xml:space="preserve">Ejegodvej 6B</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H129">
-        <v>587</v>
+        <v>1046</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311390832</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,35 +7771,35 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Kongemarksvej 20</t>
+          <t xml:space="preserve">Kraghave Møllevej 44</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5433538</t>
+          <t xml:space="preserve">9859610</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H130">
-        <v>691</v>
+        <v>1166</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372895</t>
+          <t xml:space="preserve">311390820</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-25</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helene Strangesvej 1</t>
+          <t xml:space="preserve">Merkurs Plads 6</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119126</t>
+          <t xml:space="preserve">5432446</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>733</v>
+        <v>1545</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381027</t>
+          <t xml:space="preserve">311390778</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-06</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helene Strangesvej 1</t>
+          <t xml:space="preserve">Sofiegade 2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119126</t>
+          <t xml:space="preserve">7825651</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>612</v>
+        <v>1003</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381027</t>
+          <t xml:space="preserve">311390824</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-06</t>
+          <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 2</t>
+          <t xml:space="preserve">Vendersgade 8</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437014</t>
+          <t xml:space="preserve">5425830</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="H133">
-        <v>2207</v>
+        <v>320</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384900</t>
+          <t xml:space="preserve">311391046</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-26</t>
+          <t xml:space="preserve">2029-08-01</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongensgade 37</t>
+          <t xml:space="preserve">Guldborgvej 27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426499</t>
+          <t xml:space="preserve">3085359</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>500</v>
+        <v>407</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390686</t>
+          <t xml:space="preserve">311392991</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammerlodden 1B</t>
+          <t xml:space="preserve">Alslevvej 25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426957</t>
+          <t xml:space="preserve">5438878</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H135">
-        <v>764</v>
+        <v>623</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390674</t>
+          <t xml:space="preserve">311421941</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-30</t>
+          <t xml:space="preserve">2030-02-11</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejegodvej 6B</t>
+          <t xml:space="preserve">Parkvej 31B</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">5437745</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>1046</v>
+        <v>5144</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390832</t>
+          <t xml:space="preserve">311424091</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurs Plads 6</t>
+          <t xml:space="preserve">Nykøbingvej 196</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,25 +8201,25 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432446</t>
+          <t xml:space="preserve">8871869</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H137">
-        <v>1545</v>
+        <v>280</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390778</t>
+          <t xml:space="preserve">311431448</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2030-04-02</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiegade 2</t>
+          <t xml:space="preserve">Idrætsalleen 2</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7825651</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H138">
-        <v>1003</v>
+        <v>890</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390824</t>
+          <t xml:space="preserve">311438857</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,17 +8311,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghave Møllevej 44</t>
+          <t xml:space="preserve">Væggerløsevej 2A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9859610</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="H139">
-        <v>1166</v>
+        <v>2572</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311390820</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-31</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,35 +8371,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendersgade 8</t>
+          <t xml:space="preserve">Væggerløsevej 2B</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425830</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H140">
-        <v>320</v>
+        <v>2111</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391046</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-01</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,35 +8431,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 27</t>
+          <t xml:space="preserve">Væggerløsevej 2C</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085359</t>
+          <t xml:space="preserve">3139869</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H141">
-        <v>407</v>
+        <v>930</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311392991</t>
+          <t xml:space="preserve">311438855</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-15</t>
+          <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alslevvej 25</t>
+          <t xml:space="preserve">Dronningensgade 24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438878</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="H142">
-        <v>623</v>
+        <v>1245</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421940</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-11</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,35 +8551,35 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 31B</t>
+          <t xml:space="preserve">Dronningensgade 26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437745</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H143">
-        <v>5144</v>
+        <v>1725</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424091</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykøbingvej 196</t>
+          <t xml:space="preserve">Dronningensgade 30</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871869</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>280</v>
+        <v>1384</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311431448</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-02</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Væggerløsevej 2A</t>
+          <t xml:space="preserve">Skolegade 3A</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">5424711</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="H145">
-        <v>2572</v>
+        <v>1470</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311473578</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Væggerløsevej 2C</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">5424710</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H146">
-        <v>930</v>
+        <v>1098</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311473586</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,35 +8791,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Væggerløsevej 2B</t>
+          <t xml:space="preserve">Byvangen 1D</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">3085399</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H147">
-        <v>2111</v>
+        <v>361</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438855</t>
+          <t xml:space="preserve">311540217</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsalleen 2</t>
+          <t xml:space="preserve">Byvangen 1E</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3139869</t>
+          <t xml:space="preserve">3085399</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H148">
-        <v>890</v>
+        <v>260</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438857</t>
+          <t xml:space="preserve">311540213</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-19</t>
+          <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 30</t>
+          <t xml:space="preserve">Nykøbingvej 54</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">5439361</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8930,16 +8930,16 @@
         </is>
       </c>
       <c r="H149">
-        <v>1384</v>
+        <v>330</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311558487</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 26</t>
+          <t xml:space="preserve">Solgårdsvej 7</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">284073, 284074</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,16 +8990,16 @@
         </is>
       </c>
       <c r="H150">
-        <v>1725</v>
+        <v>1427</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311558490</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningensgade 24</t>
+          <t xml:space="preserve">Solgårdsvej 7</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">284074</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>1245</v>
+        <v>1850</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311558489</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,35 +9091,35 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Solgårdsvej 7</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424710</t>
+          <t xml:space="preserve">284073</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H152">
-        <v>1098</v>
+        <v>344</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473586</t>
+          <t xml:space="preserve">311558757</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2031-10-30</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,17 +9151,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3A</t>
+          <t xml:space="preserve">Aastrupvej 82</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424711</t>
+          <t xml:space="preserve">3125916</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,16 +9170,16 @@
         </is>
       </c>
       <c r="H153">
-        <v>1470</v>
+        <v>506</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311473578</t>
+          <t xml:space="preserve">311564854</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-06</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,17 +9211,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvangen 1D</t>
+          <t xml:space="preserve">Linde Alle 42</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085399</t>
+          <t xml:space="preserve">3087923</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,16 +9230,16 @@
         </is>
       </c>
       <c r="H154">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540217</t>
+          <t xml:space="preserve">311564851</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,35 +9271,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvangen 1E</t>
+          <t xml:space="preserve">Ndr Ringvej 6</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3085399</t>
+          <t xml:space="preserve">5431315</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>260</v>
+        <v>722</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540213</t>
+          <t xml:space="preserve">311564856</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-11</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykøbingvej 54</t>
+          <t xml:space="preserve">Nykøbingvej 116</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5439361</t>
+          <t xml:space="preserve">3118927</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,16 +9350,16 @@
         </is>
       </c>
       <c r="H156">
-        <v>330</v>
+        <v>536</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558487</t>
+          <t xml:space="preserve">311564852</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-29</t>
+          <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linde Alle 42</t>
+          <t xml:space="preserve">Nykøbingvej 198B</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,20 +9401,20 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3087923</t>
+          <t xml:space="preserve">8871869</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H157">
-        <v>391</v>
+        <v>2059</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564851</t>
+          <t xml:space="preserve">311564848</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykøbingvej 116</t>
+          <t xml:space="preserve">Nørre Boulevard 4A</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118927</t>
+          <t xml:space="preserve">5432442</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,11 +9470,11 @@
         </is>
       </c>
       <c r="H158">
-        <v>536</v>
+        <v>7108</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564852</t>
+          <t xml:space="preserve">311564841</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9511,30 +9511,30 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aastrupvej 82</t>
+          <t xml:space="preserve">Nørre Boulevard 4A</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3125916</t>
+          <t xml:space="preserve">5432442</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159">
-        <v>506</v>
+        <v>1983</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564854</t>
+          <t xml:space="preserve">311564843</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 1B</t>
+          <t xml:space="preserve">Sophieholmen 17</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4871</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3129021</t>
+          <t xml:space="preserve">5428292</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9590,11 +9590,11 @@
         </is>
       </c>
       <c r="H160">
-        <v>1837</v>
+        <v>1217</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564853</t>
+          <t xml:space="preserve">311564855</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9631,17 +9631,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophieholmen 17</t>
+          <t xml:space="preserve">Sportsvej 1B</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4871</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5428292</t>
+          <t xml:space="preserve">3129021</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9650,11 +9650,11 @@
         </is>
       </c>
       <c r="H161">
-        <v>1217</v>
+        <v>1837</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564855</t>
+          <t xml:space="preserve">311564853</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Ringvej 6</t>
+          <t xml:space="preserve">Københavnsvej 5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431315</t>
+          <t xml:space="preserve">5431330</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,16 +9710,16 @@
         </is>
       </c>
       <c r="H162">
-        <v>722</v>
+        <v>1210</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564856</t>
+          <t xml:space="preserve">311565973</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 4A</t>
+          <t xml:space="preserve">Københavnsvej 5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,25 +9761,25 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432442</t>
+          <t xml:space="preserve">5431330</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>7108</v>
+        <v>341</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564841</t>
+          <t xml:space="preserve">311565974</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Boulevard 4A</t>
+          <t xml:space="preserve">Møllebakken 5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432442</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,16 +9830,16 @@
         </is>
       </c>
       <c r="H164">
-        <v>1983</v>
+        <v>674</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564843</t>
+          <t xml:space="preserve">311566078</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykøbingvej 198B</t>
+          <t xml:space="preserve">Møllebakken 5</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8871869</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H165">
-        <v>2059</v>
+        <v>674</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564848</t>
+          <t xml:space="preserve">311566080</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-29</t>
+          <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,30 +9931,30 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 17B</t>
+          <t xml:space="preserve">Møllebakken 5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4863</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116630</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H166">
-        <v>2220</v>
+        <v>734</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565965</t>
+          <t xml:space="preserve">311566081</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 97</t>
+          <t xml:space="preserve">Møllebakken 7</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,20 +10001,20 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5430816</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H167">
-        <v>326</v>
+        <v>1479</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565968</t>
+          <t xml:space="preserve">311565975</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 97</t>
+          <t xml:space="preserve">Møllebakken 9</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,20 +10061,20 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5430816</t>
+          <t xml:space="preserve">5431321</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>350</v>
+        <v>622</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565969</t>
+          <t xml:space="preserve">311566010</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10111,30 +10111,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 9</t>
+          <t xml:space="preserve">Nr Alslev Parkvej 7</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H169">
-        <v>622</v>
+        <v>810</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566010</t>
+          <t xml:space="preserve">311566084</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,30 +10171,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 5</t>
+          <t xml:space="preserve">Nørregade 17B</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4863</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">3116630</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>674</v>
+        <v>2220</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566078</t>
+          <t xml:space="preserve">311565965</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,30 +10231,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 5</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H171">
-        <v>674</v>
+        <v>1404</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566080</t>
+          <t xml:space="preserve">311566082</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,30 +10291,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 5</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H172">
-        <v>734</v>
+        <v>1239</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566081</t>
+          <t xml:space="preserve">311566086</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,30 +10351,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebakken 7</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431321</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H173">
-        <v>1479</v>
+        <v>878</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565975</t>
+          <t xml:space="preserve">311566083</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,30 +10411,30 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 5</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431330</t>
+          <t xml:space="preserve">9861656</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H174">
-        <v>1210</v>
+        <v>1556</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565973</t>
+          <t xml:space="preserve">311566085</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 5</t>
+          <t xml:space="preserve">Østre Alle 97</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10481,20 +10481,20 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431330</t>
+          <t xml:space="preserve">5430816</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H175">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565974</t>
+          <t xml:space="preserve">311565968</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,30 +10531,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Østre Alle 97</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">5430816</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H176">
-        <v>1404</v>
+        <v>350</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566082</t>
+          <t xml:space="preserve">311565969</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,35 +10591,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Skolegade 3C</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">5424711</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H177">
-        <v>1239</v>
+        <v>1000</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566086</t>
+          <t xml:space="preserve">311566185</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,35 +10651,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Engestoftevej 112</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">3086118</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H178">
-        <v>878</v>
+        <v>1333</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566083</t>
+          <t xml:space="preserve">311568463</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nr Alslev Parkvej 7</t>
+          <t xml:space="preserve">Skolegade 3</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10726,20 +10726,20 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H179">
-        <v>810</v>
+        <v>2392</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566084</t>
+          <t xml:space="preserve">311568276</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Vendsysselvej 2A</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">5429328</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>1556</v>
+        <v>350</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566085</t>
+          <t xml:space="preserve">311568279</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-03</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3C</t>
+          <t xml:space="preserve">Vendsysselvej 2A</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5424711</t>
+          <t xml:space="preserve">5429328</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,16 +10850,16 @@
         </is>
       </c>
       <c r="H181">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566185</t>
+          <t xml:space="preserve">311568278</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,17 +10891,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engestoftevej 112</t>
+          <t xml:space="preserve">Voldgade 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3086118</t>
+          <t xml:space="preserve">5425032</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,11 +10910,11 @@
         </is>
       </c>
       <c r="H182">
-        <v>1333</v>
+        <v>1778</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568463</t>
+          <t xml:space="preserve">311568282</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10966,15 +10966,15 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H183">
-        <v>1778</v>
+        <v>556</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568282</t>
+          <t xml:space="preserve">311568283</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voldgade 1</t>
+          <t xml:space="preserve">Østre Alle 97</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,20 +11021,20 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425032</t>
+          <t xml:space="preserve">5430816</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H184">
-        <v>556</v>
+        <v>284</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568283</t>
+          <t xml:space="preserve">311568288</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendsysselvej 2A</t>
+          <t xml:space="preserve">Østre Alle 97</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,20 +11081,20 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429328</t>
+          <t xml:space="preserve">5430816</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H185">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568279</t>
+          <t xml:space="preserve">311568274</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vendsysselvej 2A</t>
+          <t xml:space="preserve">Egevænget 1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,25 +11141,25 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429328</t>
+          <t xml:space="preserve">5429769</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H186">
-        <v>350</v>
+        <v>1484</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568278</t>
+          <t xml:space="preserve">311570424</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 97</t>
+          <t xml:space="preserve">Lindevænget 1</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,25 +11201,25 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5430816</t>
+          <t xml:space="preserve">5429769</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H187">
-        <v>284</v>
+        <v>1115</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568288</t>
+          <t xml:space="preserve">311570423</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 97</t>
+          <t xml:space="preserve">Lindevænget 1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,25 +11261,25 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5430816</t>
+          <t xml:space="preserve">5429769</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H188">
-        <v>261</v>
+        <v>1495</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568274</t>
+          <t xml:space="preserve">311570423</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,35 +11311,35 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 3</t>
+          <t xml:space="preserve">Lindevænget 1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861656</t>
+          <t xml:space="preserve">5429769</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H189">
-        <v>2392</v>
+        <v>779</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568276</t>
+          <t xml:space="preserve">311570423</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-16</t>
+          <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevænget 1</t>
+          <t xml:space="preserve">Lindevænget 1B</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11446,11 +11446,11 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H191">
-        <v>1115</v>
+        <v>1493</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevænget 1</t>
+          <t xml:space="preserve">Københavnsvej 7</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11501,25 +11501,25 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429769</t>
+          <t xml:space="preserve">5431339</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>1495</v>
+        <v>696</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570423</t>
+          <t xml:space="preserve">311584140</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevænget 1</t>
+          <t xml:space="preserve">Københavnsvej 9</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,25 +11561,25 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429769</t>
+          <t xml:space="preserve">5431340</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>1484</v>
+        <v>1074</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570424</t>
+          <t xml:space="preserve">311584141</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevænget 1</t>
+          <t xml:space="preserve">Københavnsvej 9</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11621,25 +11621,25 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429769</t>
+          <t xml:space="preserve">5431340</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H194">
-        <v>779</v>
+        <v>1608</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570423</t>
+          <t xml:space="preserve">311584142</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevænget 1B</t>
+          <t xml:space="preserve">Thorsensvej 11A</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5429769</t>
+          <t xml:space="preserve">5426713</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H195">
-        <v>1493</v>
+        <v>894</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570423</t>
+          <t xml:space="preserve">311592261</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-04</t>
+          <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 7</t>
+          <t xml:space="preserve">Thorsensvej 11B</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,25 +11741,25 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431339</t>
+          <t xml:space="preserve">5426713</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H196">
-        <v>696</v>
+        <v>483</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584140</t>
+          <t xml:space="preserve">311592262</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-10</t>
+          <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 9</t>
+          <t xml:space="preserve">Thorsensvej 11D</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11801,25 +11801,25 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431340</t>
+          <t xml:space="preserve">5426713</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H197">
-        <v>1074</v>
+        <v>1758</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584141</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-10</t>
+          <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 9</t>
+          <t xml:space="preserve">Thorsensvej 11G</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11861,25 +11861,25 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5431340</t>
+          <t xml:space="preserve">5426713</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H198">
-        <v>1608</v>
+        <v>2359</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584142</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-10</t>
+          <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,17 +11911,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsensvej 11A</t>
+          <t xml:space="preserve">Tyreholmen 2</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426713</t>
+          <t xml:space="preserve">7070028</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -11930,16 +11930,16 @@
         </is>
       </c>
       <c r="H199">
-        <v>894</v>
+        <v>380</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592261</t>
+          <t xml:space="preserve">311595275</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-11</t>
+          <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,17 +11971,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsensvej 11B</t>
+          <t xml:space="preserve">Tyreholmen 2</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426713</t>
+          <t xml:space="preserve">7070028</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11990,16 +11990,16 @@
         </is>
       </c>
       <c r="H200">
-        <v>483</v>
+        <v>380</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592262</t>
+          <t xml:space="preserve">311595275</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-11</t>
+          <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12031,35 +12031,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsensvej 11D</t>
+          <t xml:space="preserve">Adelgade 22D</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426713</t>
+          <t xml:space="preserve">5432801</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H201">
-        <v>1758</v>
+        <v>332</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311598252</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-11</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,35 +12091,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsensvej 11G</t>
+          <t xml:space="preserve">Møllestræde 3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5426713</t>
+          <t xml:space="preserve">5438675</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H202">
-        <v>2359</v>
+        <v>308</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311598256</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-11</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyreholmen 2</t>
+          <t xml:space="preserve">Gl. Landevej 1</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070028</t>
+          <t xml:space="preserve">5438921</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -12170,16 +12170,16 @@
         </is>
       </c>
       <c r="H203">
-        <v>380</v>
+        <v>1785</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595275</t>
+          <t xml:space="preserve">311601329</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-26</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,35 +12211,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyreholmen 2</t>
+          <t xml:space="preserve">Idrætsalleen 1</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7070028</t>
+          <t xml:space="preserve">8923613</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H204">
-        <v>380</v>
+        <v>1056</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595275</t>
+          <t xml:space="preserve">311601326</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-26</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12271,35 +12271,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adelgade 22D</t>
+          <t xml:space="preserve">Idrætsalleen 1</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4873</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432801</t>
+          <t xml:space="preserve">8923613</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H205">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598249</t>
+          <t xml:space="preserve">311601326</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllestræde 3</t>
+          <t xml:space="preserve">Præstemarken 86A</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438675</t>
+          <t xml:space="preserve">9113302</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,16 +12350,16 @@
         </is>
       </c>
       <c r="H206">
-        <v>308</v>
+        <v>914</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598256</t>
+          <t xml:space="preserve">311602192</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,17 +12391,17 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 1</t>
+          <t xml:space="preserve">Rådhusgade 6</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5438921</t>
+          <t xml:space="preserve">5437394</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -12410,16 +12410,16 @@
         </is>
       </c>
       <c r="H207">
-        <v>1785</v>
+        <v>559</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601329</t>
+          <t xml:space="preserve">311602191</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,17 +12451,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsalleen 1</t>
+          <t xml:space="preserve">Guldborghave 102A</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4862</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">8923613</t>
+          <t xml:space="preserve">3083012</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,16 +12470,16 @@
         </is>
       </c>
       <c r="H208">
-        <v>1056</v>
+        <v>536</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601326</t>
+          <t xml:space="preserve">311603710</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-05-29</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,17 +12511,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsalleen 1</t>
+          <t xml:space="preserve">Nørregade 21B</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4873</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8923613</t>
+          <t xml:space="preserve">5425509</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12530,16 +12530,16 @@
         </is>
       </c>
       <c r="H209">
-        <v>556</v>
+        <v>1739</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601326</t>
+          <t xml:space="preserve">311605488</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-06-06</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 6</t>
+          <t xml:space="preserve">Juniorsgade 35</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437394</t>
+          <t xml:space="preserve">5436979</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12590,16 +12590,16 @@
         </is>
       </c>
       <c r="H210">
-        <v>559</v>
+        <v>2621</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602191</t>
+          <t xml:space="preserve">311609233</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-22</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12631,17 +12631,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 86A</t>
+          <t xml:space="preserve">Kettingevej 61A</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4892</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113302</t>
+          <t xml:space="preserve">3082296</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -12650,16 +12650,16 @@
         </is>
       </c>
       <c r="H211">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311602192</t>
+          <t xml:space="preserve">311609230</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-22</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12691,17 +12691,17 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborghave 102A</t>
+          <t xml:space="preserve">Præsteparken 1A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4862</t>
+          <t xml:space="preserve">4894</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3083012</t>
+          <t xml:space="preserve">3091013</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12710,16 +12710,16 @@
         </is>
       </c>
       <c r="H212">
-        <v>536</v>
+        <v>441</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603710</t>
+          <t xml:space="preserve">311609231</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-29</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 21B</t>
+          <t xml:space="preserve">Præsteparken 1A</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4894</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425509</t>
+          <t xml:space="preserve">3091013</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -12770,16 +12770,16 @@
         </is>
       </c>
       <c r="H213">
-        <v>1739</v>
+        <v>422</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605488</t>
+          <t xml:space="preserve">311609232</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-06</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettingevej 61A</t>
+          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4892</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3082296</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -12830,16 +12830,16 @@
         </is>
       </c>
       <c r="H214">
-        <v>905</v>
+        <v>444</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609230</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12871,35 +12871,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præsteparken 1A</t>
+          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4894</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091013</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H215">
-        <v>441</v>
+        <v>287</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609231</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12931,35 +12931,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præsteparken 1A</t>
+          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4894</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091013</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H216">
-        <v>422</v>
+        <v>496</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609232</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -12991,35 +12991,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juniorsgade 35</t>
+          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5436979</t>
+          <t xml:space="preserve">8727516</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H217">
-        <v>2621</v>
+        <v>1245</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609233</t>
+          <t xml:space="preserve">311611205</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -13051,35 +13051,35 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
+          <t xml:space="preserve">Kalkbrænderivej 17</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="H218">
-        <v>444</v>
+        <v>517</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13111,35 +13111,35 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
+          <t xml:space="preserve">Kalkbrænderivej 22</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="H219">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13171,17 +13171,17 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
+          <t xml:space="preserve">Nørrevang 17</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13190,16 +13190,16 @@
         </is>
       </c>
       <c r="H220">
-        <v>496</v>
+        <v>2143</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615356</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13231,35 +13231,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghave Gaabensevej 100</t>
+          <t xml:space="preserve">Nørrevang 19</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727516</t>
+          <t xml:space="preserve">7828315</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H221">
-        <v>1245</v>
+        <v>1396</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311611205</t>
+          <t xml:space="preserve">311615354</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-28</t>
+          <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24</t>
+          <t xml:space="preserve">Nørrevang 21A</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13306,15 +13306,15 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H222">
-        <v>330</v>
+        <v>1380</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615359</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 21A</t>
+          <t xml:space="preserve">Nørrevang 24</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13366,15 +13366,15 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H223">
-        <v>1380</v>
+        <v>330</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 19</t>
+          <t xml:space="preserve">Nørrevang 24</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13426,15 +13426,15 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H224">
-        <v>1396</v>
+        <v>300</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615354</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 17</t>
+          <t xml:space="preserve">Nørrevang 24</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13486,15 +13486,15 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H225">
-        <v>2143</v>
+        <v>469</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615356</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24A</t>
+          <t xml:space="preserve">Nørrevang 24</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13546,11 +13546,11 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H226">
-        <v>717</v>
+        <v>304</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24</t>
+          <t xml:space="preserve">Nørrevang 24A</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13606,11 +13606,11 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H227">
-        <v>300</v>
+        <v>717</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalkbrænderivej 22</t>
+          <t xml:space="preserve">Nørrevang 24D</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13786,11 +13786,11 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H230">
-        <v>293</v>
+        <v>714</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -13831,35 +13831,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24D</t>
+          <t xml:space="preserve">Parkvej 37</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4800</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">5432176</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H231">
-        <v>714</v>
+        <v>9644</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311621577</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-14</t>
+          <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13891,35 +13891,35 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalkbrænderivej 17</t>
+          <t xml:space="preserve">Kirkevej 21K</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4872</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">3132020</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H232">
-        <v>517</v>
+        <v>780</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311635811</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-14</t>
+          <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -13951,35 +13951,35 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24</t>
+          <t xml:space="preserve">Stationspladsen 2A</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">9972154</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H233">
-        <v>469</v>
+        <v>724</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311635794</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-14</t>
+          <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -14011,35 +14011,35 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevang 24</t>
+          <t xml:space="preserve">Præstemarken 100A</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">7828315</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H234">
-        <v>304</v>
+        <v>784</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311643821</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-14</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -14071,35 +14071,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 37</t>
+          <t xml:space="preserve">Præstemarken 102A</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4800</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5432176</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H235">
-        <v>9644</v>
+        <v>784</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311621577</t>
+          <t xml:space="preserve">311643823</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-19</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -14131,35 +14131,35 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 21K</t>
+          <t xml:space="preserve">Præstemarken 104A</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4872</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3132020</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H236">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635811</t>
+          <t xml:space="preserve">311643824</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-14</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14191,17 +14191,17 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationspladsen 2A</t>
+          <t xml:space="preserve">Præstemarken 90</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4840</t>
+          <t xml:space="preserve">4850</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9972154</t>
+          <t xml:space="preserve">9764676</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -14210,16 +14210,16 @@
         </is>
       </c>
       <c r="H237">
-        <v>724</v>
+        <v>521</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635795</t>
+          <t xml:space="preserve">311643816</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-14</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 90</t>
+          <t xml:space="preserve">Præstemarken 92A</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14266,15 +14266,15 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H238">
-        <v>521</v>
+        <v>1064</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643816</t>
+          <t xml:space="preserve">311643817</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 92A</t>
+          <t xml:space="preserve">Præstemarken 96A</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14326,15 +14326,15 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H239">
-        <v>1064</v>
+        <v>784</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643817</t>
+          <t xml:space="preserve">311643819</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 96A</t>
+          <t xml:space="preserve">Præstemarken 98A</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H240">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643819</t>
+          <t xml:space="preserve">311643820</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14431,35 +14431,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 98A</t>
+          <t xml:space="preserve">Kirkevej 21</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4872</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">3132005</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H241">
-        <v>784</v>
+        <v>1858</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643820</t>
+          <t xml:space="preserve">311645850</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14491,35 +14491,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 100A</t>
+          <t xml:space="preserve">Syrenvænget 62A</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">9725887</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H242">
-        <v>784</v>
+        <v>729</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643821</t>
+          <t xml:space="preserve">311645849</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -14551,35 +14551,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 102A</t>
+          <t xml:space="preserve">Syrenvænget 62C</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">9725887</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H243">
-        <v>784</v>
+        <v>1856</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643823</t>
+          <t xml:space="preserve">311645849</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14611,35 +14611,35 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarken 104A</t>
+          <t xml:space="preserve">Kalkbrænderivej 5</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4850</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9764676</t>
+          <t xml:space="preserve">282930, 282931, 282932</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H244">
-        <v>784</v>
+        <v>4824</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643824</t>
+          <t xml:space="preserve">311651096</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -14671,17 +14671,17 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 21</t>
+          <t xml:space="preserve">Solgårdsvej 5</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4872</t>
+          <t xml:space="preserve">4880</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3132005</t>
+          <t xml:space="preserve">3079884</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -14690,16 +14690,16 @@
         </is>
       </c>
       <c r="H245">
-        <v>1858</v>
+        <v>330</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645850</t>
+          <t xml:space="preserve">311697414</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14731,17 +14731,17 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrenvænget 62A</t>
+          <t xml:space="preserve">Agervej 2</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4990</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725887</t>
+          <t xml:space="preserve">5437545</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -14750,16 +14750,16 @@
         </is>
       </c>
       <c r="H246">
-        <v>729</v>
+        <v>1266</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645849</t>
+          <t xml:space="preserve">311730401</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14791,35 +14791,35 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrenvænget 62C</t>
+          <t xml:space="preserve">Skovvej 26</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9725887</t>
+          <t xml:space="preserve">284140, 284141</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H247">
-        <v>1856</v>
+        <v>2360</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645849</t>
+          <t xml:space="preserve">311746899</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -14851,17 +14851,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 5</t>
+          <t xml:space="preserve">Skerrisvej 24</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880</t>
+          <t xml:space="preserve">4840</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3079884</t>
+          <t xml:space="preserve">284142, 284143</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -14870,16 +14870,16 @@
         </is>
       </c>
       <c r="H248">
-        <v>330</v>
+        <v>2707</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311697414</t>
+          <t xml:space="preserve">311747829</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-01</t>
+          <t xml:space="preserve">2034-03-25</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 2</t>
+          <t xml:space="preserve">Åmarksvej 5A</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4990</t>
+          <t xml:space="preserve">4891</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5437545</t>
+          <t xml:space="preserve">281195</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -14930,16 +14930,16 @@
         </is>
       </c>
       <c r="H249">
-        <v>1266</v>
+        <v>1490</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730401</t>
+          <t xml:space="preserve">311765634</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-06-11</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">

--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -4134,7 +4134,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054697</t>
+          <t xml:space="preserve">100248354</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421941</t>
+          <t xml:space="preserve">311421939</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598252</t>
+          <t xml:space="preserve">311598249</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615354</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635794</t>
+          <t xml:space="preserve">311635795</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">

--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L250"/>
+  <dimension ref="A1:M250"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2014-08-16</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-17</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-01</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-12</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-26</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-12</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-13</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-14</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-21</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-25</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-01</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-10</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Damgaard Rådgivende Ingeniører</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-16</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-03</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-11-22</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-03-27</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-03</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-16</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-27</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-09</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-08-16</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-04</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-09-10</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-01</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-10-24</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-14</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-04</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-08</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-01</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-08</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-25</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-06</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-06-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-30</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-31</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-01</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-15</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8094,20 +8764,25 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421939</t>
+          <t xml:space="preserve">311421940</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-11</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-02</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-19</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">IGS Rådgivende Ingeniører ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-06</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-11</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-29</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-30</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-29</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-03</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-16</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-10</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11694,20 +12664,25 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592261</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11814,20 +12794,25 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11874,20 +12859,25 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-11</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-26</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12054,20 +13054,25 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598249</t>
+          <t xml:space="preserve">311598252</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-22</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-29</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-06</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-28</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13074,20 +14159,25 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13134,20 +14224,25 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13194,20 +14289,25 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615356</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13254,20 +14354,25 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615354</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13314,20 +14419,25 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615359</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13374,20 +14484,25 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13434,20 +14549,25 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13494,20 +14614,25 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13554,20 +14679,25 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13614,20 +14744,25 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13674,20 +14809,25 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13734,20 +14874,25 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13794,20 +14939,25 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-07-14</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-19</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13974,20 +15134,25 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635795</t>
+          <t xml:space="preserve">311635794</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-14</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-01</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-25</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-11</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,21 +16244,26 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-16</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L250"/>
+  <autoFilter ref="A1:M250"/>
 </worksheet>
 </file>
--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -8764,7 +8764,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311421940</t>
+          <t xml:space="preserve">311421939</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592261</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -12859,12 +12859,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598252</t>
+          <t xml:space="preserve">311598249</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14289,12 +14289,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615356</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14809,7 +14809,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
